--- a/cod/oltp_to_olap/data/metadata/legenda.xlsx
+++ b/cod/oltp_to_olap/data/metadata/legenda.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucac\Desktop\licenta\cod\oltp_to_olap\data\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC7E88F-7A1E-42CF-A9A7-33864448219F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C979A5C-7373-4A80-B190-4DD6AC233CFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -542,7 +542,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -565,6 +565,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -634,19 +639,19 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -703,7 +708,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CF596D4-E0CD-4C7F-9835-06D1B9A77906}" name="Table1" displayName="Table1" ref="A2:C16" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CF596D4-E0CD-4C7F-9835-06D1B9A77906}" name="Table1" displayName="Table1" ref="A2:C16" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A2:C16" xr:uid="{9CF596D4-E0CD-4C7F-9835-06D1B9A77906}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{25C0C9DC-CFFD-4E2D-B4F2-0E7F52DF4374}" name="Cod modificat" dataDxfId="2"/>
@@ -1040,25 +1045,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+    <row r="7" spans="1:3" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:3" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="23" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1129,13 +1134,13 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="23" t="s">
         <v>6</v>
       </c>
     </row>
